--- a/Result/profitability/9907.xlsx
+++ b/Result/profitability/9907.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>0.26</v>
       </c>
       <c r="M2" t="n">
-        <v>0.29125</v>
+        <v>0.2775</v>
       </c>
       <c r="N2" t="n">
-        <v>13.12125</v>
+        <v>12.87125</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.46</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3125</v>
+        <v>0.30375</v>
       </c>
       <c r="N3" t="n">
-        <v>14.0475</v>
+        <v>13.93</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.43</v>
       </c>
       <c r="M4" t="n">
-        <v>0.335</v>
+        <v>0.305</v>
       </c>
       <c r="N4" t="n">
-        <v>14.94125</v>
+        <v>14.29375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.43</v>
       </c>
       <c r="M5" t="n">
-        <v>0.22875</v>
+        <v>0.20875</v>
       </c>
       <c r="N5" t="n">
-        <v>11.5825</v>
+        <v>11.12</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.13</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2025</v>
+        <v>0.18</v>
       </c>
       <c r="N6" t="n">
-        <v>11.40125</v>
+        <v>11.03</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.14</v>
       </c>
       <c r="M7" t="n">
-        <v>0.175</v>
+        <v>0.1675</v>
       </c>
       <c r="N7" t="n">
-        <v>11.30625</v>
+        <v>11.19125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.26</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1775</v>
+        <v>0.17875</v>
       </c>
       <c r="N8" t="n">
-        <v>12.105</v>
+        <v>12.12125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9907</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>10732</v>
+      </c>
+      <c r="D75" t="n">
+        <v>9569</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1163</v>
+      </c>
+      <c r="F75" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="G75" t="n">
+        <v>512</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.77%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>512</v>
+      </c>
+      <c r="K75" t="n">
+        <v>287</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>12.7875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.009999999999999981</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.0588235294117645</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.129999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.0121381886087768</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.4705882352941178</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.699999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2544704264099037</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
